--- a/invoice_automation/clients/northsky_comm/templates/TAXCenterLookup.xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/TAXCenterLookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHONCODE\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AE0E1D-33CD-4AC7-9F29-AD4CB251C777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAC76E0-F1FB-47AB-86BA-E5D988CCF95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -348,13 +348,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -362,15 +362,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>97140</v>
       </c>
       <c r="B2">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3806712660</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>97333</v>
       </c>
@@ -378,7 +378,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>95336</v>
       </c>
@@ -386,7 +386,7 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>95382</v>
       </c>
@@ -394,12 +394,28 @@
         <v>123456</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>97330</v>
       </c>
       <c r="B6">
         <v>123456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>98683</v>
+      </c>
+      <c r="B7">
+        <v>4801107800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>95826</v>
+      </c>
+      <c r="B8">
+        <v>506736560</v>
       </c>
     </row>
   </sheetData>
